--- a/nr-add-examples/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-29T16:00:10+00:00</t>
+    <t>2025-04-30T07:38:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T07:38:18+00:00</t>
+    <t>2025-04-30T07:39:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T07:39:59+00:00</t>
+    <t>2025-04-30T07:55:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T07:55:10+00:00</t>
+    <t>2025-04-30T08:28:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T08:28:31+00:00</t>
+    <t>2025-04-30T11:32:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-pdsm-ext-is-archived.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T11:32:46+00:00</t>
+    <t>2025-04-30T11:36:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
